--- a/USME_Salesforce_Sprint_Release_Plan_3Weeks.xlsx
+++ b/USME_Salesforce_Sprint_Release_Plan_3Weeks.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -18,8 +18,11 @@
     <sheet name="Approval Tier Matrix" sheetId="3" r:id="rId3"/>
     <sheet name="Queries" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,6 +30,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -768,15 +773,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -993,39 +998,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G1000"/>
-  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18.265625" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="45" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="35" customWidth="1"/>
-    <col min="8" max="26" width="8.73046875" customWidth="1"/>
+    <col min="8" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7" ht="14.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:7" ht="14.25">
       <c r="C3" s="1"/>
@@ -4194,23 +4199,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E1000"/>
-  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="26" width="8.73046875" customWidth="1"/>
+    <col min="6" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="3" spans="1:5" ht="25.5" customHeight="1">
       <c r="A3" s="13" t="s">
@@ -5459,22 +5464,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D1000"/>
-  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="26" width="8.73046875" customWidth="1"/>
+    <col min="5" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="3" spans="1:4" ht="25.5" customHeight="1">
       <c r="A3" s="13" t="s">
@@ -6541,14 +6546,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.86328125" customWidth="1"/>
-    <col min="2" max="2" width="107.53125" customWidth="1"/>
+    <col min="1" max="1" width="5.85546875" customWidth="1"/>
+    <col min="2" max="2" width="107.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>144</v>
       </c>
       <c r="B1" s="26"/>
